--- a/pensum/ol18/OL18_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol18/OL18_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="172">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 18: Personalpolitikk, rekruttering og medarbeidersamtaler (V5)</t>
   </si>
@@ -194,12 +194,36 @@
     <t xml:space="preserve">c)  Utkastet hang fire uker uten kvalifiserte søkere, og så lenge står stillingen ubesatt. Hvor mange kroner i fakturering uteblir på de fire ukene? 1 200 timer ÷ 52 uker × 4 uker × 890 kr.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tapt fakturering = fakturerbare timer per år / 52 × antall uker × timepris. Timetall og timepris er fra Nordlys' faktaark; kostnaden ved tom stilling er casens tall, ikke bokas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Kari sier: «Lappen henger der alle ansatte ser den, så loven er oppfylt.» Hva er riktig?   A: Ja. § 14-1 er oppfylt, og da er utlysningen ferdig   B: § 14-1 er oppfylt overfor de ansatte, men lappen når ingen søkere utenfor huset   C: Nei. § 14-1 gir de ansatte fortrinnsrett, så stillingen kan ikke lyses ut eksternt   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Skriv en ny overskrift. Hva bør Kari rette først, hva må inn i annonsen, og i hvilke kanaler bør den lyses ut? Tre–fire setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk bokas krav til annonsen og kanalene (18.2.3), behovsanalysen (18.2.2) og lovgrensene fra a. Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fem ting kan en annonse ikke kreve eller spørre om: alder, kjønn, etnisitet, helse utover det jobben krever, og graviditet eller planer om barn. Hvilke linjer treffer de fem?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tallet og kanalen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timer i uka: 1 200 / 52. Gang med 4 uker og 890 kr. For d: § 14-1 handler om de ansatte. Når lappen noen som ikke jobber hos Nordlys?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 18, avsnitt 18.2.2 (behovsanalyse) og 18.2.3 (utlysning og annonsen). Arbeidsmiljøloven §§ 9-3, 13-1, 13-2 og 14-1; likestillings- og diskrimineringsloven §§ 6, 29 og 30. Annonseutkastet er fra v4, øvingsheftet og appen. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -293,12 +317,30 @@
     <t xml:space="preserve">c)  Hvor mange kroner i fakturering uteblir for hver måned stillingen står ubesatt? 1 400 timer ÷ 12 × 890 kr.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tapt fakturering per måned = fakturerbare timer per år / 12 × timepris. Tallene er Fjells (1 400 timer, 890 kr); regnestykket er casens, ikke bokas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Sist søkte ingen på annonsen i lokalavisa. Hva sier boka at Mona bør gjøre nå?   A: Vente til arbeidsmarkedet snur; det finnes ingen montører   B: Utlyse i medier som når søkerne: fagpresse, nett, NAV, jobbmesser og utdanningsinstitusjoner, lærlingen via skolene   C: Gjøre annonsen kortere og billigere, så flere ser den   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Skriv overskriften og fire ting annonsen for montøren må si. Hvordan kan den samtidig markedsføre Fjell? Tre–fire setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk kravene til annonsen og markedsføring av bedriften (18.2.3) og behovsanalysen (18.2.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trinn 1 og 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hvem i Fjell kunne fått en ny montørstilling? Boka sier intern rekruttering er lettest i større bedrifter. I behovsanalysen: hva trenger stillingen, og hva er bare den perfekte kandidaten?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Måneden og kanalen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 400 / 12 timer i måneden, ganger 890 kr. Hvem leser lokalavisa, og hvor finner du montører og lærlinger? Se bokas liste over medier i 18.2.3.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 18, avsnitt 18.2.1 (stilling ledig, internt eller eksternt), 18.2.2 (behovsanalyse) og 18.2.3 (utlysning). Arbeidsmiljøloven §§ 13-1 og 14-1, likestillings- og diskrimineringsloven § 6. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -347,9 +389,15 @@
     <t xml:space="preserve">a)  Hvor mange timer bruker Ronny på sine 7 samtaler, når hver tar to timer og han forbereder seg én time til hver?</t>
   </si>
   <si>
+    <t xml:space="preserve">Ledertid = antall samtaler × (samtaletid + forberedelse). Begrepet bak er at personalpolitikken må brytes ned i rutiner, og at linjelederne må sette av tid (Organisasjon og ledelse 18.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange kroner i fakturering bruker de 12 montørene på samtalene, med to timer samtale og én time forberedelse hver, til 890 kr?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kostnad i fakturering = antall montører × timer per montør × timepris. Timetall og timepris er Nordlys' faktaark; kostnaden er casens, ikke bokas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Ja eller nei: er punktet i Ronnys plan for samtalen med Sara i tråd med det boka sier om medarbeidersamtalen?</t>
   </si>
   <si>
@@ -374,6 +422,21 @@
     <t xml:space="preserve">e)  Hva må Kari og lederne gjøre for at de 17 samtalene ikke blir skuebrød? Bruk minst ett tall og bokas forutsetninger. Tre–fire setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk de fire kravene, forutsetningene og skuebrødsadvarselen (18.3) og kravet om at policy får tid (18.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ronny: 7 samtaler × (2 timer + 1 time forberedelse). Montørene: 12 × 3 timer × 890 kr. Lærlingene regnes ikke som fakturerbare.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kravene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boka har fire krav: klart formål, planlagt og forberedt av begge, jobbrelatert, fortrolig og personlig. Og: samtalen må ikke skape forventninger som ikke kan innfris.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 18, avsnitt 18.1 (policy brutt ned i rutiner) og 18.3 (medarbeidersamtalen: fire krav, seks spørsmål, forutsetninger, skuebrød). Ledere og antall: faktaarket, OL11 og OL14. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -455,10 +518,25 @@
     <t xml:space="preserve">c)  Hvor mange kroner i fakturering koster fadderordningen de fire første ukene? 1 400 timer ÷ 52 uker × 4 uker × 20 % × 890 kr.</t>
   </si>
   <si>
+    <t xml:space="preserve">Kostnad = timer per år / 52 × uker × andel × timepris. Tallene er Fjells; regnestykket er casens. Fadderordningen er fra Organisasjon og ledelse 18.2.7.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Hvem bør være fadder for den nye montøren, etter det boka sier om fadderen?   A: Mona, fordi hun er faglig ansvarlig og vet mest   B: Montør 1: samme nivå, sosialt trygg og har selv vært ny i Fjell nylig   C: Montør 2, fordi han jobber mest effektivt og ikke blir forstyrret   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Lag en skisse til introduksjonsprogram for de to nye. Hvem har ansvaret, hva skjer de første ukene, og hvordan bør programmet for lærlingen skille seg fra montørens? Tre–fire setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk introduksjon og fadder (18.2.7), Hersey og Blanchard (17.5.3), medarbeidersamtalen (18.3) og lovens frister fra a og b. Lovteksten er ikke kontrollert mot Lovdata; kontroller mot lovdata.no før bruk.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prøvetid: inntil seks måneder, skriftlig (§ 15-6). Avtale: senest sju dager (§ 14-5). Frist i prøvetiden: 14 dager (§ 15-3). Oppsigelse: tilpasning, dyktighet eller pålitelighet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fadderen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 400 / 52 × 4 × 0,20 × 890. Boka: fadderen er på samme nivå, har sosiale ferdigheter og fersk erfaring med å være ny. Hvem er på samme nivå som den nye?</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 18, avsnitt 18.2.7 (introduksjon, fadder, nyutdannet og erfaren) og kap. 17.5.3 (Hersey og Blanchard). Arbeidsmiljøloven §§ 14-5, 14-6 første ledd bokstav f, 14-9, 15-3 sjuende ledd og 15-6. Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -472,7 +550,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -539,8 +617,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -556,13 +656,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -615,7 +733,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -688,7 +806,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -733,8 +871,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -748,7 +886,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -762,7 +900,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1065,7 +1203,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1331,80 +1469,143 @@
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="17" t="str">
-        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
+      <c r="B29" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-    </row>
-    <row r="35" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="21"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+    </row>
+    <row r="43" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="23">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A17:G17"/>
@@ -1418,11 +1619,16 @@
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A31:G33"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1439,7 +1645,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1450,7 +1656,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1460,7 +1666,7 @@
     </row>
     <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1471,7 +1677,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1482,10 +1688,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -1494,11 +1700,11 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>65</v>
+      <c r="A8" s="24" t="s">
+        <v>73</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1507,11 +1713,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>67</v>
+      <c r="A9" s="24" t="s">
+        <v>75</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1520,11 +1726,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>69</v>
+      <c r="A10" s="24" t="s">
+        <v>77</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1533,11 +1739,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>71</v>
+      <c r="A11" s="24" t="s">
+        <v>79</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1546,11 +1752,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>73</v>
+      <c r="A12" s="24" t="s">
+        <v>81</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1559,11 +1765,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>75</v>
+      <c r="A13" s="24" t="s">
+        <v>83</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1572,11 +1778,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>77</v>
+      <c r="A14" s="24" t="s">
+        <v>85</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1585,11 +1791,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>79</v>
+      <c r="A15" s="24" t="s">
+        <v>87</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1614,7 +1820,7 @@
     </row>
     <row r="18" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1628,7 +1834,7 @@
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1637,7 +1843,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1651,7 +1857,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1665,7 +1871,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1679,7 +1885,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1693,7 +1899,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1707,7 +1913,7 @@
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1719,80 +1925,143 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-    </row>
-    <row r="32" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+    </row>
+    <row r="40" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1813,11 +2082,16 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1834,7 +2108,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1845,7 +2119,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1855,7 +2129,7 @@
     </row>
     <row r="4" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1866,7 +2140,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1877,77 +2151,77 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="20" t="n">
+        <v>111</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" s="21" t="n">
+        <v>112</v>
+      </c>
+      <c r="B9" s="26" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="20" t="n">
+        <v>113</v>
+      </c>
+      <c r="B10" s="25" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="B11" s="21" t="n">
+        <v>114</v>
+      </c>
+      <c r="B11" s="26" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="20" t="n">
+        <v>115</v>
+      </c>
+      <c r="B12" s="25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B13" s="21" t="n">
+        <v>116</v>
+      </c>
+      <c r="B13" s="26" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="B14" s="25" t="n">
         <v>890</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="B15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B16" s="14"/>
     </row>
@@ -1979,7 +2253,7 @@
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1991,88 +2265,58 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="17" t="str">
-        <f aca="false">IF(F21="","",IF(ABS(F21-(32040))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="16"/>
+      <c r="F23" s="14"/>
       <c r="G23" s="17" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="17" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F23="","",IF(ABS(F23-(32040))&lt;=1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -2084,9 +2328,9 @@
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -2094,87 +2338,199 @@
       <c r="E28" s="7"/>
       <c r="F28" s="16"/>
       <c r="G28" s="17" t="str">
-        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-    </row>
-    <row r="34" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="17" t="str">
+        <f aca="false">IF(F32="","",IF(UPPER(TRIM(F32))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+    </row>
+    <row r="44" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="23">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A30:G32"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2191,7 +2547,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2202,7 +2558,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2212,7 +2568,7 @@
     </row>
     <row r="4" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2223,7 +2579,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2234,10 +2590,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -2246,11 +2602,11 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
-        <v>69</v>
+      <c r="A8" s="24" t="s">
+        <v>77</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2259,11 +2615,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
-        <v>121</v>
+      <c r="A9" s="24" t="s">
+        <v>142</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2272,11 +2628,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
-        <v>123</v>
+      <c r="A10" s="24" t="s">
+        <v>144</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2285,11 +2641,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
-        <v>125</v>
+      <c r="A11" s="24" t="s">
+        <v>146</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2298,11 +2654,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
-        <v>127</v>
+      <c r="A12" s="24" t="s">
+        <v>148</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2311,11 +2667,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>129</v>
+      <c r="A13" s="24" t="s">
+        <v>150</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2324,11 +2680,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
-        <v>131</v>
+      <c r="A14" s="24" t="s">
+        <v>152</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2337,11 +2693,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
-        <v>133</v>
+      <c r="A15" s="24" t="s">
+        <v>154</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2366,7 +2722,7 @@
     </row>
     <row r="18" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2380,7 +2736,7 @@
     </row>
     <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2389,7 +2745,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -2403,7 +2759,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2417,7 +2773,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2431,7 +2787,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2445,7 +2801,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2459,7 +2815,7 @@
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2471,80 +2827,143 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-    </row>
-    <row r="32" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+    </row>
+    <row r="40" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2565,11 +2984,16 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ol18/OL18_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol18/OL18_Klasseoppgaver_v5.xlsx
@@ -92,7 +92,7 @@
     <t xml:space="preserve">25 minutter · Helst alene. Sammen med sidemannen eller flere hvis du vil. Ark og blyant, appen (PC eller mobil) eller læreboka.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Stillingsannonsens viktigste funksjon er å tiltrekke kvalifiserte søkere og samtidig sile ut dem bedriften ikke er interessert i (18.2.3). Overskriften skal vise stillingstype og kompetanse, og annonsen skal si noe om ansvar og arbeidsområder, plassering i organisasjonen, lønn, reise, søknadsfrist og kontaktperson. Den må utlyses i medier som når fram til søkerne. Loven setter grenser: alder (aml § 13-1, jf. § 13-2 første ledd bokstav a), kjønn og etnisitet (ldl § 6, jf. § 29 bokstav a), helseopplysninger utover det arbeidet krever (aml § 9-3) og graviditet, adopsjon eller planer om barn (ldl § 30 bokstav a). Aml § 14-1 gir de ansatte rett til å få vite om ledige stillinger, ikke rett til å få dem.</t>
+    <t xml:space="preserve">Kort oppsummert: Stillingsannonsens viktigste funksjon er å tiltrekke kvalifiserte søkere og samtidig sile ut dem bedriften ikke er interessert i (18.2.3). Overskriften skal vise stillingstype og kompetanse, og annonsen skal si noe om ansvar og arbeidsområder, plassering i organisasjonen, lønn, reise, søknadsfrist og kontaktperson. Den må utlyses i medier som når fram til søkerne. Loven setter grenser: alder (arbeidsmiljøloven § 13-1, se § 13-2 første ledd bokstav a), kjønn og etnisitet (likestillings- og diskrimineringsloven § 6, se § 29 bokstav a), helseopplysninger utover det arbeidet krever (arbeidsmiljøloven § 9-3) og graviditet, adopsjon eller planer om barn (likestillings- og diskrimineringsloven § 30 bokstav a). Arbeidsmiljøloven § 14-1 gir de ansatte rett til å få vite om ledige stillinger, ikke rett til å få dem.</t>
   </si>
   <si>
     <t xml:space="preserve">Casen er lagt til 2026/2027. Solcelle og lading har to montører og ingen leder. Kari har vurdert å løse det internt, med en av solcellemontørene, Ronny eller Tom, men har bestemt seg for å ansette en arbeidende avdelingsleder: en som leder avdelingen og selv står på anlegg, med 1 200 fakturerbare timer i året som de andre montørene. Timeprisen er 890 kr. Karis første utkast til annonse hang fire uker som lapp på oppslagstavla i pauserommet, og ingen kvalifiserte søkte. Linjene i utkastet står i tabellen. Gå fram slik: les hver linje mot loven og mot bokas krav til annonsen, regn hva de fire ukene kostet i fakturering som uteblir, og skriv til slutt hva Kari bør rette først.</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">Timer i uka: 1 200 / 52. Gang med 4 uker og 890 kr. For d: § 14-1 handler om de ansatte. Når lappen noen som ikke jobber hos Nordlys?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 18, avsnitt 18.2.2 (behovsanalyse) og 18.2.3 (utlysning og annonsen). Arbeidsmiljøloven §§ 9-3, 13-1, 13-2 og 14-1; likestillings- og diskrimineringsloven §§ 6, 29 og 30. Annonseutkastet er fra v4, øvingsheftet og appen. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 18, avsnitt 18.2.2 (behovsanalyse) og 18.2.3 (utlysning og annonsen). Arbeidsmiljøloven §§ 9-3, 13-1, 13-2 og 14-1; likestillings- og diskrimineringsloven §§ 6, 29 og 30. Annonseutkastet er fra versjon 4, øvingsheftet og appen. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">Regnearket er øvingsstøtte. Det kan ikke siteres eller vises til i besvarelser, prosjektoppgaver eller eksamen; der gjelder læreboka og oppgitte primærkilder.</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">Timepris</t>
   </si>
   <si>
-    <t xml:space="preserve">890 kr uten mva</t>
+    <t xml:space="preserve">890 kr uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Etterspørsel</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">Boka har fire krav: klart formål, planlagt og forberedt av begge, jobbrelatert, fortrolig og personlig. Og: samtalen må ikke skape forventninger som ikke kan innfris.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 18, avsnitt 18.1 (policy brutt ned i rutiner) og 18.3 (medarbeidersamtalen: fire krav, seks spørsmål, forutsetninger, skuebrød). Ledere og antall: faktaarket, OL11 og OL14. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 18, avsnitt 18.1 (policy brutt ned i rutiner) og 18.3 (medarbeidersamtalen: fire krav, seks spørsmål, forutsetninger, skuebrød). Ledere og antall: faktaarket, kap. 11 og 14. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B2 · Fjell Elektro: de første seks månedene</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Enhver bedrift bør ha et introduksjonsprogram, og ansvaret ligger hos den nyansattes nærmeste overordnede (18.2.7). Programmet må være strukturert og detaljert, særlig i begynnelsen. Fadderen bør være på samme nivå, ha visse sosiale ferdigheter og gjerne fersk erfaring med å være ny. En nyutdannet trenger mer støtte enn en med erfaring. Loven: fast ansettelse er hovedregelen (aml § 14-9); skriftlig arbeidsavtale senest sju dager etter at arbeidsforholdet begynte når det varer over en måned (§ 14-5); prøvetid inntil seks måneder, avtalt skriftlig (§§ 14-6 første ledd bokstav f og 15-6), med 14 dagers oppsigelsesfrist om ikke annet er avtalt (§ 15-3 sjuende ledd). Oppsigelse i prøvetiden må begrunnes i tilpasning til arbeidet, faglig dyktighet eller pålitelighet.</t>
+    <t xml:space="preserve">Kort oppsummert: Enhver bedrift bør ha et introduksjonsprogram, og ansvaret ligger hos den nyansattes nærmeste overordnede (18.2.7). Programmet må være strukturert og detaljert, særlig i begynnelsen. Fadderen bør være på samme nivå, ha visse sosiale ferdigheter og gjerne fersk erfaring med å være ny. En nyutdannet trenger mer støtte enn en med erfaring. Loven: fast ansettelse er hovedregelen (arbeidsmiljøloven § 14-9); skriftlig arbeidsavtale senest sju dager etter at arbeidsforholdet begynte når det varer over en måned (§ 14-5); prøvetid inntil seks måneder, avtalt skriftlig (§§ 14-6 første ledd bokstav f og 15-6), med 14 dagers oppsigelsesfrist om ikke annet er avtalt (§ 15-3 sjuende ledd). Oppsigelse i prøvetiden må begrunnes i tilpasning til arbeidet, faglig dyktighet eller pålitelighet.</t>
   </si>
   <si>
     <t xml:space="preserve">Mona har ansatt en montør med seks års erfaring fra en annen installatør, og en lærling som kommer rett fra skolen. Montøren begynner en mandag, fast ansatt. Mona vil ha prøvetid og et introduksjonsprogram, og hun lurer på hvem av de to montørene som skal være fadder. Montør 1 vil planlegge selv og snakke med kundene; montør 2 vil helst få arbeidsordren og jobbe i fred. Begge har vært i Fjell siden starten. Fadderen skal bruke 20 % av sine fakturerbare timer på den nye de fire første ukene. En montør har 1 400 fakturerbare timer i året, og timeprisen er 890 kr. Gå fram slik: avklar prøvetid og arbeidsavtale etter loven, regn hva fadderordningen koster, velg fadder etter boka, og lag til slutt et introduksjonsprogram for begge de nye.</t>
@@ -1222,7 +1222,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="123.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>

--- a/pensum/ol18/OL18_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol18/OL18_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="172">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 18: Personalpolitikk, rekruttering og medarbeidersamtaler (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 18: Personalpolitikk, rekruttering og medarbeidersamtaler (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ol18/OL18_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol18/OL18_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Stillingsannonsens viktigste funksjon er å tiltrekke kvalifiserte søkere og samtidig sile ut dem bedriften ikke er interessert i (18.2.3). Overskriften skal vise stillingstype og kompetanse, og annonsen skal si noe om ansvar og arbeidsområder, plassering i organisasjonen, lønn, reise, søknadsfrist og kontaktperson. Den må utlyses i medier som når fram til søkerne. Loven setter grenser: alder (arbeidsmiljøloven § 13-1, se § 13-2 første ledd bokstav a), kjønn og etnisitet (likestillings- og diskrimineringsloven § 6, se § 29 bokstav a), helseopplysninger utover det arbeidet krever (arbeidsmiljøloven § 9-3) og graviditet, adopsjon eller planer om barn (likestillings- og diskrimineringsloven § 30 bokstav a). Arbeidsmiljøloven § 14-1 gir de ansatte rett til å få vite om ledige stillinger, ikke rett til å få dem.</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Solcelle og lading har to montører og ingen leder. Kari har vurdert å løse det internt, med en av solcellemontørene, Ronny eller Tom, men har bestemt seg for å ansette en arbeidende avdelingsleder: en som leder avdelingen og selv står på anlegg, med 1 200 fakturerbare timer i året som de andre montørene. Timeprisen er 890 kr. Karis første utkast til annonse hang fire uker som lapp på oppslagstavla i pauserommet, og ingen kvalifiserte søkte. Linjene i utkastet står i tabellen. Gå fram slik: les hver linje mot loven og mot bokas krav til annonsen, regn hva de fire ukene kostet i fakturering som uteblir, og skriv til slutt hva Kari bør rette først.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Solcelle og lading har to montører og ingen leder. Kari har vurdert å løse det internt, med en av solcellemontørene, Ronny eller Tom, men har bestemt seg for å ansette en arbeidende avdelingsleder: en som leder avdelingen og selv står på anlegg, med 1 200 fakturerbare timer i året som de andre montørene. Timeprisen Nordlys tar av kunden, er 890 kr uten merverdiavgift (faktaarket). Karis første utkast til annonse hang fire uker som lapp på oppslagstavla i pauserommet, og ingen kvalifiserte søkte. Linjene i utkastet står i tabellen. Gå fram slik: les hver linje mot loven og mot bokas krav til annonsen, regn hva de fire ukene kostet i fakturering som uteblir, og skriv til slutt hva Kari bør rette først.</t>
   </si>
   <si>
     <t xml:space="preserve">Linje</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">Kort oppsummert: På trinn 1 avgjør bedriften om stillingen skal besettes, og om den skal rekruttere internt eller eksternt (18.2.1). Intern rekruttering er ofte lettere i større bedrifter, med egne programmer for opplæring og forfremmelse. Behovsanalysen (18.2.2) tar for seg faglige kvalifikasjoner og personlige egenskaper; den kan lett ende som en beskrivelse av den perfekte kandidaten. Utlysningen (18.2.3) må skje i medier som når fram til potensielle søkere: internett, dagspresse, fagpresse, oppslagstavler, NAV og bemanningsbyråer, jobbmesser, bedriftspresentasjoner og utdanningsinstitusjoner.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS har gått ett år. Mona Fjell er eier, daglig leder og faglig ansvarlig, og har to montører. Hun skal ansette én montør og én lærling, slik at Fjell blir fem personer. Fjell har flere forespørsler enn de rekker, så en ny montør med 1 400 fakturerbare timer i året vil fakturere fullt fra han er i gang. Timeprisen er 890 kr. Sist Mona lyste ut, med en annonse i lokalavisa, søkte ingen. Bransjen mangler fagarbeidere. Gå fram slik: ta trinn 1 (internt eller eksternt), lag behovsanalysen, regn hva en måned uten montør koster, og vurder til slutt kanaler og innhold i annonsen.</t>
+    <t xml:space="preserve">Fjell Elektro AS har gått ett år. Mona Fjell er eier, daglig leder og faglig ansvarlig, og har to montører. Hun skal ansette én montør og én lærling, slik at Fjell blir fem personer. Fjell har flere forespørsler enn de rekker, så en ny montør med 1 400 fakturerbare timer i året vil fakturere fullt fra han er i gang. Timeprisen Fjell tar av kunden, er 890 kr (Fjells faktaark). Sist Mona lyste ut, med en annonse i lokalavisa, søkte ingen. Bransjen mangler fagarbeidere. Gå fram slik: ta trinn 1 (internt eller eksternt), lag behovsanalysen, regn hva en måned uten montør koster, og vurder til slutt kanaler og innhold i annonsen.</t>
   </si>
   <si>
     <t xml:space="preserve">Forutsetning</t>
